--- a/artfynd/A 19007-2023 artfynd.xlsx
+++ b/artfynd/A 19007-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113792899</v>
+        <v>113793449</v>
       </c>
       <c r="B2" t="n">
-        <v>90753</v>
+        <v>56953</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,13 +713,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Valleredsskog, Vg</t>
@@ -761,7 +766,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +776,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +785,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113793122</v>
+        <v>113793425</v>
       </c>
       <c r="B3" t="n">
-        <v>56826</v>
+        <v>56955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,29 +819,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -882,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113793449</v>
+        <v>113792899</v>
       </c>
       <c r="B4" t="n">
-        <v>56953</v>
+        <v>90753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,25 +939,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -957,18 +965,13 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valleredsskog, Vg</t>
@@ -1010,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,6 +1032,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1047,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113793425</v>
+        <v>113793122</v>
       </c>
       <c r="B5" t="n">
-        <v>56955</v>
+        <v>56826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,33 +1067,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 19007-2023 artfynd.xlsx
+++ b/artfynd/A 19007-2023 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113793425</v>
+        <v>113793122</v>
       </c>
       <c r="B3" t="n">
-        <v>56955</v>
+        <v>56826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,33 +819,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -890,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113792899</v>
+        <v>113793425</v>
       </c>
       <c r="B4" t="n">
-        <v>90753</v>
+        <v>56955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,25 +935,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6031</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -965,23 +961,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Valleredsskog, Vg</t>
+          <t>Vallered s, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333558</v>
+        <v>333452</v>
       </c>
       <c r="R4" t="n">
-        <v>6433752</v>
+        <v>6433725</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1029,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1051,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113793122</v>
+        <v>113792899</v>
       </c>
       <c r="B5" t="n">
-        <v>56826</v>
+        <v>90753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,46 +1059,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallered s, Vg</t>
+          <t>Valleredsskog, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>333452</v>
+        <v>333558</v>
       </c>
       <c r="R5" t="n">
-        <v>6433725</v>
+        <v>6433752</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,7 +1133,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1143,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,6 +1152,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 19007-2023 artfynd.xlsx
+++ b/artfynd/A 19007-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
